--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ64"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5443,45 +5443,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103795</v>
+        <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626797</v>
+        <v>626729</v>
       </c>
       <c r="R46" t="n">
-        <v>7217132</v>
+        <v>7217208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5508,12 +5513,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,66 +5533,67 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103795</t>
+          <t>https://artportalen.se/Sighting/137152928</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103796</v>
+        <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626803</v>
+        <v>626781</v>
       </c>
       <c r="R47" t="n">
-        <v>7217099</v>
+        <v>7216981</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,12 +5620,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5634,66 +5640,67 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103796</t>
+          <t>https://artportalen.se/Sighting/137152931</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103797</v>
+        <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626820</v>
+        <v>626832</v>
       </c>
       <c r="R48" t="n">
-        <v>7217037</v>
+        <v>7217100</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,12 +5727,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5740,28 +5747,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103797</t>
+          <t>https://artportalen.se/Sighting/137152933</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103798</v>
+        <v>128103795</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5796,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626811</v>
+        <v>626797</v>
       </c>
       <c r="R49" t="n">
-        <v>7217065</v>
+        <v>7217132</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5861,13 +5864,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103798</t>
+          <t>https://artportalen.se/Sighting/128103795</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103799</v>
+        <v>128103796</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5902,10 +5905,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626796</v>
+        <v>626803</v>
       </c>
       <c r="R50" t="n">
-        <v>7217064</v>
+        <v>7217099</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5967,13 +5970,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103799</t>
+          <t>https://artportalen.se/Sighting/128103796</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103800</v>
+        <v>128103797</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6008,10 +6011,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626843</v>
+        <v>626820</v>
       </c>
       <c r="R51" t="n">
-        <v>7217062</v>
+        <v>7217037</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6073,13 +6076,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103800</t>
+          <t>https://artportalen.se/Sighting/128103797</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103802</v>
+        <v>128103798</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6114,10 +6117,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626806</v>
+        <v>626811</v>
       </c>
       <c r="R52" t="n">
-        <v>7217042</v>
+        <v>7217065</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6179,13 +6182,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103802</t>
+          <t>https://artportalen.se/Sighting/128103798</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103803</v>
+        <v>128103799</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6220,10 +6223,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626709</v>
+        <v>626796</v>
       </c>
       <c r="R53" t="n">
-        <v>7217057</v>
+        <v>7217064</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6285,13 +6288,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103803</t>
+          <t>https://artportalen.se/Sighting/128103799</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103804</v>
+        <v>128103800</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6326,10 +6329,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626622</v>
+        <v>626843</v>
       </c>
       <c r="R54" t="n">
-        <v>7217121</v>
+        <v>7217062</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6391,13 +6394,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103804</t>
+          <t>https://artportalen.se/Sighting/128103800</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103805</v>
+        <v>128103802</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6432,10 +6435,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626744</v>
+        <v>626806</v>
       </c>
       <c r="R55" t="n">
-        <v>7217285</v>
+        <v>7217042</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6497,13 +6500,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103805</t>
+          <t>https://artportalen.se/Sighting/128103802</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103814</v>
+        <v>128103803</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6538,10 +6541,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626811</v>
+        <v>626709</v>
       </c>
       <c r="R56" t="n">
-        <v>7217114</v>
+        <v>7217057</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6603,13 +6606,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103814</t>
+          <t>https://artportalen.se/Sighting/128103803</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103815</v>
+        <v>128103804</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6644,10 +6647,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626821</v>
+        <v>626622</v>
       </c>
       <c r="R57" t="n">
-        <v>7217074</v>
+        <v>7217121</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6709,13 +6712,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103815</t>
+          <t>https://artportalen.se/Sighting/128103804</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103816</v>
+        <v>128103805</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -6750,10 +6753,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626837</v>
+        <v>626744</v>
       </c>
       <c r="R58" t="n">
-        <v>7217076</v>
+        <v>7217285</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6815,13 +6818,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103816</t>
+          <t>https://artportalen.se/Sighting/128103805</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128103817</v>
+        <v>128103814</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -6856,10 +6859,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>626705</v>
+        <v>626811</v>
       </c>
       <c r="R59" t="n">
-        <v>7217045</v>
+        <v>7217114</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6921,13 +6924,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103817</t>
+          <t>https://artportalen.se/Sighting/128103814</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128103818</v>
+        <v>128103815</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -6962,10 +6965,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626631</v>
+        <v>626821</v>
       </c>
       <c r="R60" t="n">
-        <v>7217081</v>
+        <v>7217074</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,13 +7030,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103818</t>
+          <t>https://artportalen.se/Sighting/128103815</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128103820</v>
+        <v>128103816</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7068,10 +7071,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626749</v>
+        <v>626837</v>
       </c>
       <c r="R61" t="n">
-        <v>7217269</v>
+        <v>7217076</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7133,13 +7136,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103820</t>
+          <t>https://artportalen.se/Sighting/128103816</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128103821</v>
+        <v>128103817</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7174,10 +7177,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626754</v>
+        <v>626705</v>
       </c>
       <c r="R62" t="n">
-        <v>7217270</v>
+        <v>7217045</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7239,16 +7242,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128103821</t>
+          <t>https://artportalen.se/Sighting/128103817</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134317513</v>
+        <v>128103818</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7276,14 +7279,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>626718</v>
+        <v>626631</v>
       </c>
       <c r="R63" t="n">
-        <v>7217256</v>
+        <v>7217081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7310,12 +7313,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7330,49 +7333,53 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134317513</t>
+          <t>https://artportalen.se/Sighting/128103818</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128103732</v>
+        <v>128103820</v>
       </c>
       <c r="B64" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7382,10 +7389,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626665</v>
+        <v>626749</v>
       </c>
       <c r="R64" t="n">
-        <v>7217113</v>
+        <v>7217269</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7446,6 +7453,320 @@
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128103820</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128103821</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>626754</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7217270</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128103821</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134317513</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>626718</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7217256</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134317513</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128103732</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>626665</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7217113</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128103732</t>
         </is>
@@ -7516,6 +7837,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5472,11 +5472,7 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
@@ -5579,11 +5575,7 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
@@ -5686,11 +5678,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>137152928</v>
       </c>
       <c r="B46" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>137152931</v>
       </c>
       <c r="B47" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>137152933</v>
       </c>
       <c r="B48" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
